--- a/3_experiments/human/irony_triggering_detection_human_ann.xlsx
+++ b/3_experiments/human/irony_triggering_detection_human_ann.xlsx
@@ -470,9 +470,7 @@
   u1: this girl is totally amazing and I'm not gonna miss the opportunity to be with her. I'm quitting my job and traveling with her!</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,9 +490,7 @@
   u1: What else could it be, really? It's either aliens or government secrets, and I think we all know which one is more likely.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -514,9 +510,7 @@
   u1: Come on, this has never happened before!</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -536,9 +530,7 @@
   u1: Thanks for lending it to me.</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -558,9 +550,7 @@
   u1: This one is really good. Come on!</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -580,9 +570,7 @@
   u1: that person should work on their English, don't you think?</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,9 +590,7 @@
   u1: I mean, she is great in many other ways, but her music taste is just horrible.</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -624,9 +610,7 @@
   u1: it's alright. I didn't even like this shirt anyway.</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -646,9 +630,7 @@
   u1: Yeah, that's never a good sign. It sounds like they're not ready to move on yet.</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -668,9 +650,7 @@
   u1: But that's the thing, she's not just any girl, she's amazing.</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -690,9 +670,7 @@
   u1: this girl is totally amazing and I'm not gonna miss the opportunity to be with her. I'm quitting my job and traveling with her!</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -712,9 +690,7 @@
   u1: why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -734,9 +710,7 @@
   u1: Look, look how shiny this watch is.</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -756,9 +730,7 @@
   u1: I don't know, man... I just feel like everyone's having so much fun without me.</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -778,9 +750,7 @@
   u1: Ha ha, no, no, I swear it's not like that! I'll return the charger and toaster before you know it. Can I please just borrow your suitcase now?</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -800,9 +770,7 @@
   u1: This joint proposal is going to be delayed yet again because of their laziness.</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -822,9 +790,7 @@
   u1: Why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -844,9 +810,7 @@
   u1: Come on, man! It's just a few days for my trip, and I'll bring both back.</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -866,9 +830,7 @@
   u1: What's wrong with that? My aunt has great taste.</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -888,9 +850,7 @@
   u1: How do I even get started with posting something?</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -910,9 +870,7 @@
   u1: I swear, Bill deserves better than someone who just takes advantage of him.</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -932,9 +890,7 @@
   u1: It really has only happened once, I swear!</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -954,9 +910,7 @@
   u1: ugh, moving is always so stressful and chaotic...</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -976,9 +930,7 @@
   u1: Ugh, someone needs to teach them about responsibility!</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -998,9 +950,7 @@
   u1: First message from Steve that directly precedes the given u2</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1020,9 +970,7 @@
   u1: I used my savings to buy Ezillion! They say it's gonna go way up in the next few months!</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1042,9 +990,7 @@
   u1: I didn't even like this shirt anyway.</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1064,9 +1010,7 @@
   u1: Yeah, it's super frustrating when they leave everything for me to handle.</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1086,9 +1030,7 @@
   u1: I mean, she is great in many other ways, but her music taste is just horrible.</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1108,9 +1050,7 @@
   u1: I guess I was just hoping you'd get it because... well, because you're my best friend, and I know how much you need a job.</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1130,9 +1070,7 @@
   u1: my shoes are more fashionable than yours. You should hear about how all the fashionable magazines actually avoid featuring black shoes.</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1152,9 +1090,7 @@
   u1: I should have just stayed at my old job. If it hadn't been for this new job, I wouldn't have had to deal with so much crap.</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1174,9 +1110,7 @@
   u1: Just kidding, I didn't break the bank... okay, fine, I might have spent a bit more than I should have</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1196,9 +1130,7 @@
   u1: I don't know, man... it just feels like I'm not making progress anywhere.</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1218,9 +1150,7 @@
   u1: why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1240,9 +1170,7 @@
   u1: Fries touching the burger again!</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1262,9 +1190,7 @@
   u1: Dude, did my advice work or what? Any progress so far?</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1284,9 +1210,7 @@
   u1: I'm telling you, it was just one time!</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1306,9 +1230,7 @@
   u1: look at me! I'm Mr. Shoehand!</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1328,9 +1250,7 @@
   u1: that person should work on their English, don't you think?</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1350,9 +1270,7 @@
   u1: Hey, that's not fair! I always mean to flush, I just get distracted</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1372,9 +1290,7 @@
   u1: I know it's a bit out there, but I'm feeling adventurous tonight</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1394,9 +1310,7 @@
   u1: Exactly! And the food itself is just amazing. The variety of flavors and textures... I was really blown away.</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1416,9 +1330,7 @@
   u1: I mean, she is great in many other ways, but her music taste is just horrible.</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1438,9 +1350,7 @@
   u1: ew, people are so inconsiderate!</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1460,9 +1370,7 @@
   u1: Come on, I'm not that old!</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1482,9 +1390,7 @@
   u1: Mind if some of my friends join?</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1504,9 +1410,7 @@
   u1: Dude, I'll try to remember to flush the toilet, okay?</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1526,9 +1430,7 @@
   u1: what can i do to help? maybe i can hire a dog walker or something?</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1548,9 +1450,7 @@
   u1: I'm really surprised my brother hasn't cut ties with him yet.</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1570,9 +1470,7 @@
   u1: Gosh, it's so frustrating that I'm the only one trying to get the stuff moving. Everyone in the group is too laid back!</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1592,9 +1490,7 @@
   u1: You're going to wake them up.</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1614,9 +1510,7 @@
   u1: Remember when we went to that sushi place downtown? They did it just like they do in Japan, with all the precision and care.</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
+      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1636,9 +1530,7 @@
   u1: I invited some other people, hope you don't mind.</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1658,9 +1550,7 @@
   u1: I don't want to be a downer, but I have to ask, have you noticed any signals that might indicate she's open to something more?</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
+      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1680,9 +1570,7 @@
   u1: Yeah, I could really use your help. Have you talked to the team from the other department yet?</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
+      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1702,9 +1590,7 @@
   u1: A French fry just touched my burger, I'm pushing them apart.</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1724,9 +1610,7 @@
   u1: Haha, no, no polka dots, just green! I'm trying to bring a little tropical vibe to the outfit.</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
+      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1746,9 +1630,7 @@
   u1: you broke them, while moving in the heavy box</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
+      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1768,9 +1650,7 @@
   u1: wow, you really should watch how you spend your money.</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1790,9 +1670,7 @@
   u1: It makes me wonder why you didn't just say no to begin with.</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
+      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1812,9 +1690,7 @@
   u1: I don't know, man, I just don't feel safe anymore.</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1834,9 +1710,7 @@
   u1: Oh man, don't be like that! It's just a tank top. You're not going to get fired over a little red fabric</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1856,9 +1730,7 @@
   u1: i was just in an accident and mine is in the shop, that's why i need your car</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1878,9 +1750,7 @@
   u1: Ugh, moving is always so stressful and chaotic...</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
+      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1900,9 +1770,7 @@
   u1: I just talked to him and he said he's been really busy. I'm sure he'll return it soon, no big deal.</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1922,9 +1790,7 @@
   u1: Do you want to go out tonight?</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1944,9 +1810,7 @@
   u1: I don't know, man... I'm just really struggling with this. I feel like a total noob.</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1966,9 +1830,7 @@
   u1: Come on, it happened like one time!</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
+      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1988,9 +1850,7 @@
   u1: Ugh my thumbs too fat</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
+      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2010,9 +1870,7 @@
   u1: I finally found one you'll like! This one is really good. Come on!</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
+      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2032,9 +1890,7 @@
   u1: why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2054,9 +1910,7 @@
   u1: I mean, she is great in many other ways, but her music taste is just horrible.</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2076,9 +1930,7 @@
   u1: I should have just stayed at my old job. If it hadn't been for this new job, I wouldn't have had to deal with so much crap.</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2098,9 +1950,7 @@
   u1: you're going to get another job, and it's going to be even better, i just know it.</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>0</v>
-      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2120,9 +1970,7 @@
   u1: Yeah, she's always sending me cool stuff, and I try to wear it out so she doesn't think I'm just hoarding it all.</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2142,9 +1990,7 @@
   u1: oh, yeah, I'll pay you back, don't worry about it</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2164,9 +2010,7 @@
   u1: I swear, it's like nobody ever listens to me! If they did, we wouldn't be in this mess right now. Frustrating doesn't even begin to cover it!</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2186,9 +2030,7 @@
   u1: Come on, u2! Just watch the video! It's not every day we get to see this kind of thing!</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2208,9 +2050,7 @@
   u1: Yeah, I'm pretty nervous, but thanks for being supportive!</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2230,9 +2070,7 @@
   u1: Why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
+      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2252,9 +2090,7 @@
   u1: now that's a unicorn!</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
+      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2274,9 +2110,7 @@
   u1: I can relate to Bill's frustrations</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2296,9 +2130,7 @@
   u1: I don't get it, why is my brother even friends with that guy? I don't get it.</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2318,9 +2150,7 @@
   u1: I'm sure Bill feels frustrated when his colleague talks loudly on the phone all day.</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
+      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2340,9 +2170,7 @@
   u1: Then you're just not sophisticated enough to appreciate the subtlety.</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2362,9 +2190,7 @@
   u1: I don't get why my brother even hangs out with him.</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2384,9 +2210,7 @@
   u1: I can let you borrow one of mine if you want.</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2406,9 +2230,7 @@
   u1: Now that's a unicorn!</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2428,9 +2250,7 @@
   u1: Gosh, it's so frustrating that I'm the only one trying to get the stuff moving. Everyone in the group is too laid back!</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
+      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2450,9 +2270,7 @@
   u1: Ah, yeah, I totally forgot to grab some stuff for Max's stayover, didn't I? Let me just check what I have in the car... oh yeah, I've got some of his food and his leash, but you're right, we should probably get some more supplies before I head out.</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2472,9 +2290,7 @@
   u1: I invited some other people, hope you don't mind.</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
+      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2494,9 +2310,7 @@
   u1: What's the hurry, mate? Can't you see I'm busy?</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2516,9 +2330,7 @@
   u1: I just tried to turn it down to 7 and you switched it to 10. This isn't funny anymore.</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
+      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2538,9 +2350,7 @@
   u1: Ah, yeah, about that... I'm really sorry, I've been meaning to return them but I just haven't gotten around to it yet.</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2560,9 +2370,7 @@
   u1: I guess what I'm saying is that I just wish she could be more into the kind of music I like. You know, we could bond over that or something.</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2582,9 +2390,7 @@
   u1: The boss asked you to go to the bank for him, right?</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2604,9 +2410,7 @@
   u1: You're so close, just make a move!</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2626,9 +2430,7 @@
   u1: Thanks for lending it to me!</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2648,9 +2450,7 @@
   u1: Can I borrow your suitcase? I need one for my trip next week.</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
+      <c r="C101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
